--- a/data_lake/reporte_cordoba_mes/dt=2026-08-07/CORDOBA_AGO26.xlsx
+++ b/data_lake/reporte_cordoba_mes/dt=2026-08-07/CORDOBA_AGO26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E35F4A-6C79-4B94-8689-23F47B3DF0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432F77AE-BE2C-4095-B427-5172994ECA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{5F8F14AC-D557-4126-B18A-7A2C1E69122F}"/>
   </bookViews>
@@ -7393,7 +7393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7866,7 +7866,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8470,7 +8470,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9079,7 +9079,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9689,7 +9689,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9975,7 +9975,7 @@
                   <c:v>232.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1</c:v>
+                  <c:v>47.1</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-1</c:v>
@@ -19934,7 +19934,9 @@
       <c r="I3" s="25">
         <v>18.3</v>
       </c>
-      <c r="J3" s="25"/>
+      <c r="J3" s="25">
+        <v>4.5</v>
+      </c>
       <c r="K3" s="25"/>
       <c r="L3" s="25"/>
       <c r="M3" s="25"/>
@@ -19962,7 +19964,7 @@
       <c r="AI3" s="34"/>
       <c r="AJ3" s="36">
         <f>SUM(E3:AI3)</f>
-        <v>18.3</v>
+        <v>22.8</v>
       </c>
       <c r="AK3" s="30">
         <v>27.817857142857147</v>
@@ -19996,7 +19998,9 @@
       <c r="I4" s="25">
         <v>35.4</v>
       </c>
-      <c r="J4" s="25"/>
+      <c r="J4" s="25">
+        <v>0</v>
+      </c>
       <c r="K4" s="25"/>
       <c r="L4" s="25"/>
       <c r="M4" s="25"/>
@@ -20058,7 +20062,9 @@
       <c r="I5" s="25">
         <v>41.5</v>
       </c>
-      <c r="J5" s="25"/>
+      <c r="J5" s="25">
+        <v>0</v>
+      </c>
       <c r="K5" s="25"/>
       <c r="L5" s="25"/>
       <c r="M5" s="25"/>
@@ -20120,7 +20126,9 @@
       <c r="I6" s="25">
         <v>8</v>
       </c>
-      <c r="J6" s="25"/>
+      <c r="J6" s="25">
+        <v>0</v>
+      </c>
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
       <c r="M6" s="25"/>
@@ -20286,7 +20294,9 @@
       <c r="I9" s="25">
         <v>0</v>
       </c>
-      <c r="J9" s="25"/>
+      <c r="J9" s="25">
+        <v>1</v>
+      </c>
       <c r="K9" s="25"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
@@ -20314,7 +20324,7 @@
       <c r="AI9" s="34"/>
       <c r="AJ9" s="36">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK9" s="30">
         <v>65.482758620689651</v>
@@ -20398,7 +20408,9 @@
       <c r="I11" s="25">
         <v>12</v>
       </c>
-      <c r="J11" s="25"/>
+      <c r="J11" s="25">
+        <v>1.4</v>
+      </c>
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
@@ -20426,7 +20438,7 @@
       <c r="AI11" s="34"/>
       <c r="AJ11" s="36">
         <f t="shared" si="0"/>
-        <v>15.2</v>
+        <v>16.599999999999998</v>
       </c>
       <c r="AK11" s="30">
         <v>19.188461538461539</v>
@@ -20445,8 +20457,12 @@
       <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
+      <c r="E12" s="24">
+        <v>0</v>
+      </c>
+      <c r="F12" s="24">
+        <v>0</v>
+      </c>
       <c r="G12" s="25">
         <v>0</v>
       </c>
@@ -20456,7 +20472,9 @@
       <c r="I12" s="25">
         <v>57.8</v>
       </c>
-      <c r="J12" s="25"/>
+      <c r="J12" s="25">
+        <v>6</v>
+      </c>
       <c r="K12" s="25"/>
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
@@ -20484,7 +20502,7 @@
       <c r="AI12" s="34"/>
       <c r="AJ12" s="36">
         <f t="shared" si="0"/>
-        <v>57.8</v>
+        <v>63.8</v>
       </c>
       <c r="AK12" s="30">
         <v>34.724137931034484</v>
@@ -20518,7 +20536,9 @@
       <c r="I13" s="25">
         <v>3</v>
       </c>
-      <c r="J13" s="25"/>
+      <c r="J13" s="25">
+        <v>2</v>
+      </c>
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
@@ -20546,7 +20566,7 @@
       <c r="AI13" s="34"/>
       <c r="AJ13" s="36">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK13" s="30"/>
     </row>
@@ -20578,7 +20598,9 @@
       <c r="I14" s="25">
         <v>56.4</v>
       </c>
-      <c r="J14" s="25"/>
+      <c r="J14" s="25">
+        <v>1</v>
+      </c>
       <c r="K14" s="25"/>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
@@ -20606,7 +20628,7 @@
       <c r="AI14" s="34"/>
       <c r="AJ14" s="36">
         <f>SUM(E14:AI14)</f>
-        <v>105.9</v>
+        <v>106.9</v>
       </c>
       <c r="AK14" s="30">
         <v>36.1</v>
@@ -20625,7 +20647,9 @@
       <c r="D15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="24"/>
+      <c r="E15" s="24">
+        <v>0</v>
+      </c>
       <c r="F15" s="24">
         <v>0</v>
       </c>
@@ -20635,8 +20659,12 @@
       <c r="H15" s="25">
         <v>0</v>
       </c>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
+      <c r="I15" s="25">
+        <v>0</v>
+      </c>
+      <c r="J15" s="25">
+        <v>31.2</v>
+      </c>
       <c r="K15" s="25"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
@@ -20664,7 +20692,7 @@
       <c r="AI15" s="34"/>
       <c r="AJ15" s="36">
         <f t="shared" si="0"/>
-        <v>18.600000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="AK15" s="30">
         <v>60.46</v>
@@ -20794,7 +20822,7 @@
       </c>
       <c r="J19" s="26">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>47.1</v>
       </c>
       <c r="K19" s="26">
         <f t="shared" si="1"/>
